--- a/board Overviews.xlsx
+++ b/board Overviews.xlsx
@@ -1,33 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a50f0f76735a0c6b/Documents/Pinball/PortalPinball-V4.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="651" documentId="8_{71A0D3BC-EF29-42BB-95C3-409B160B156F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24EF187F-A088-495E-8559-76E6C3FE6403}"/>
+  <xr:revisionPtr revIDLastSave="876" documentId="8_{71A0D3BC-EF29-42BB-95C3-409B160B156F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{867FCC44-6632-46D6-A4F2-BC4C86B65262}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="725" activeTab="1" xr2:uid="{992D9940-FEE0-4AED-9001-DC6BE0040B0B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="725" activeTab="3" xr2:uid="{992D9940-FEE0-4AED-9001-DC6BE0040B0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Modes" sheetId="11" r:id="rId1"/>
     <sheet name="Ball devices" sheetId="12" r:id="rId2"/>
-    <sheet name="LEDs" sheetId="10" r:id="rId3"/>
-    <sheet name="Cobrapin - Game Funtion" sheetId="8" r:id="rId4"/>
-    <sheet name="PSOC4200 - Game Function" sheetId="7" r:id="rId5"/>
-    <sheet name="---" sheetId="9" r:id="rId6"/>
-    <sheet name="Cobrapin - Doc" sheetId="5" r:id="rId7"/>
-    <sheet name="PSOC4200 - Config" sheetId="6" r:id="rId8"/>
-    <sheet name="PSOC4200 - Doc" sheetId="1" r:id="rId9"/>
-    <sheet name="Coil" sheetId="2" r:id="rId10"/>
-    <sheet name="Switch" sheetId="4" r:id="rId11"/>
-    <sheet name="Incand" sheetId="3" r:id="rId12"/>
+    <sheet name="Notes on devices" sheetId="14" r:id="rId3"/>
+    <sheet name="not used yet" sheetId="13" r:id="rId4"/>
+    <sheet name="LEDs" sheetId="10" r:id="rId5"/>
+    <sheet name="Cobrapin - Game Funtion" sheetId="8" r:id="rId6"/>
+    <sheet name="PSOC4200 - Game Function" sheetId="7" r:id="rId7"/>
+    <sheet name="---" sheetId="9" r:id="rId8"/>
+    <sheet name="Cobrapin - Doc" sheetId="5" r:id="rId9"/>
+    <sheet name="PSOC4200 - Config" sheetId="6" r:id="rId10"/>
+    <sheet name="PSOC4200 - Doc" sheetId="1" r:id="rId11"/>
+    <sheet name="Coil" sheetId="2" r:id="rId12"/>
+    <sheet name="Switch" sheetId="4" r:id="rId13"/>
+    <sheet name="Incand" sheetId="3" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">LEDs!$B$1:$E$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">LEDs!$B$1:$E$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -72,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="463">
   <si>
     <t>PSOC4200</t>
   </si>
@@ -1305,9 +1307,6 @@
     <t>s-portal-m</t>
   </si>
   <si>
-    <t>Up</t>
-  </si>
-  <si>
     <t>Draw</t>
   </si>
   <si>
@@ -1341,9 +1340,6 @@
     <t>Vuk5</t>
   </si>
   <si>
-    <t>Capture ball for multi ball (feed at rear?)</t>
-  </si>
-  <si>
     <t>Capture ball for multi ball: incinerator</t>
   </si>
   <si>
@@ -1353,39 +1349,21 @@
     <t>Capture ball for multi ball: ball dropper (feed via diverter)</t>
   </si>
   <si>
-    <t>Div</t>
-  </si>
-  <si>
     <t>Divert ball to ball dropper</t>
   </si>
   <si>
-    <t>Servo</t>
-  </si>
-  <si>
     <t>Release ball from ball dropper</t>
   </si>
   <si>
-    <t>Bsv</t>
-  </si>
-  <si>
     <t>Ball saver</t>
   </si>
   <si>
-    <t>hardware</t>
-  </si>
-  <si>
-    <t>Drop post</t>
-  </si>
-  <si>
     <t>catapult</t>
   </si>
   <si>
     <t>high vuk</t>
   </si>
   <si>
-    <t>vuk</t>
-  </si>
-  <si>
     <t>Diverter</t>
   </si>
   <si>
@@ -1393,6 +1371,138 @@
   </si>
   <si>
     <t>ball saver</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>On playfield</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>BSv1</t>
+  </si>
+  <si>
+    <t>Ser1</t>
+  </si>
+  <si>
+    <t>Div1</t>
+  </si>
+  <si>
+    <t>Up1</t>
+  </si>
+  <si>
+    <t>fix wiring</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Check subway</t>
+  </si>
+  <si>
+    <t>Hardware</t>
+  </si>
+  <si>
+    <t>vuk with cover</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>drop post, normal low</t>
+  </si>
+  <si>
+    <t>simple vuk</t>
+  </si>
+  <si>
+    <t>edit exit 3d part</t>
+  </si>
+  <si>
+    <t>Drp1</t>
+  </si>
+  <si>
+    <t>Drp2</t>
+  </si>
+  <si>
+    <t>Drop targets (2) to protect exit (turret prints)</t>
+  </si>
+  <si>
+    <t>modified 3 target bank</t>
+  </si>
+  <si>
+    <t>Capture ball for multi ball (feed between popbumpers) (infront of 3rd flipper)</t>
+  </si>
+  <si>
+    <t>Drop target in front of incinarator</t>
+  </si>
+  <si>
+    <t>1 drop target</t>
+  </si>
+  <si>
+    <t>Add connector</t>
+  </si>
+  <si>
+    <t>add guide rail</t>
+  </si>
+  <si>
+    <t>remove 1 target</t>
+  </si>
+  <si>
+    <t>In design</t>
+  </si>
+  <si>
+    <t>Up2</t>
+  </si>
+  <si>
+    <t>Protect secrect entrance to right from middle portal</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>Test which switch would work best</t>
+  </si>
+  <si>
+    <t>sopranos pinball updown post boat ramp</t>
+  </si>
+  <si>
+    <t>gilligan's island island lock assembly</t>
+  </si>
+  <si>
+    <t>Outlane Kicker Assembly SS Bally/Williams (gebruikt)</t>
+  </si>
+  <si>
+    <t>1 Drop Target Bank Williams (gebruikt)</t>
+  </si>
+  <si>
+    <t>To protect from counter current from spool</t>
+  </si>
+  <si>
+    <t>black = GND</t>
+  </si>
+  <si>
+    <t>50V</t>
+  </si>
+  <si>
+    <t>Up3</t>
+  </si>
+  <si>
+    <t>Up4</t>
+  </si>
+  <si>
+    <t>tall drop post, normal high</t>
+  </si>
+  <si>
+    <t>lock assembly</t>
+  </si>
+  <si>
+    <t>kickback</t>
   </si>
 </sst>
 </file>
@@ -1443,7 +1553,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1507,6 +1617,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1635,7 +1751,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1741,6 +1857,8 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1757,12 +1875,19 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1776,6 +1901,511 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>343137</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>127215</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B62A8494-B654-1408-FC68-B84EEC830D50}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="368300"/>
+          <a:ext cx="4610337" cy="4178515"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2" descr="Outlane Kicker Assembly SS  Bally/Williams (gebruikt)">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59B116D6-A9D9-F97E-9896-635BDFC11617}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="21098" t="21773" r="29190" b="23699"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5880100" y="730250"/>
+          <a:ext cx="2184400" cy="1797050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>120650</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>463550</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3" descr="What is Diode - Definition, Diode Symbol, Types of Diode ...">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F59E6135-7334-EBA5-07F1-199E25E1E27F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="12860" t="10886" r="11418"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9874250" y="768350"/>
+          <a:ext cx="4000500" cy="2197099"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>501650</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4283480" cy="405432"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="TextBox 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFA7B0D0-25EA-B6AB-D15C-17F901AB9330}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9645650" y="1638300"/>
+          <a:ext cx="4283480" cy="405432"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2000" kern="1200">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Pinball coil:</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2000" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> GND			50V</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-NL" sz="2000" kern="1200">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1977336" cy="311496"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{706FEE51-96EB-0CC8-2173-362FF43A2B71}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9474200" y="768350"/>
+          <a:ext cx="1977336" cy="311496"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" kern="1200">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Normal to allow current:</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-NL" sz="1400" kern="1200">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>381001</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>29621</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>82925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58B33C51-9F2B-9063-6669-0580F86F015B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="381001" y="330200"/>
+          <a:ext cx="3306220" cy="4356475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>50095</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFFBB5BA-1140-4CC0-FEBE-4D73FDE21265}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5124450" y="400050"/>
+          <a:ext cx="2240845" cy="4019550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>603250</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>260552</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>177998</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{767E4581-4260-5073-F211-E843D9C4B63C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8528050" y="565150"/>
+          <a:ext cx="3924502" cy="3848298"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4" descr="Outlane Kicker Assembly SS  Bally/Williams (gebruikt)">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C63D25E-3478-49B4-AEEC-1CF84C254FB0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="21098" t="21773" r="29190" b="23699"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9772650" y="4610100"/>
+          <a:ext cx="2184400" cy="1797050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1898,7 +2528,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2125,7 +2755,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2191,7 +2821,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2257,7 +2887,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2323,7 +2953,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2389,8 +3019,24 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{389BBB06-165B-4BB1-BC39-B095B68F6B0C}" name="Table1" displayName="Table1" ref="A1:H30" totalsRowShown="0">
+  <autoFilter ref="A1:H30" xr:uid="{389BBB06-165B-4BB1-BC39-B095B68F6B0C}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H14">
+    <sortCondition ref="A1:A30"/>
+  </sortState>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{C7E715AA-7EA9-412A-9588-981395991C66}" name="Draw" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{2BD81B39-A2AC-4CCD-B6B2-ABC4C6A90DE3}" name="Code-name"/>
+    <tableColumn id="3" xr3:uid="{261BCA07-E41A-4BB4-A2CE-06E4EE6AC813}" name="Function"/>
+    <tableColumn id="4" xr3:uid="{5C749FF2-2177-4BEE-BB52-47D3402FB6B9}" name="Hardware"/>
+    <tableColumn id="5" xr3:uid="{40DAEEFC-916B-44F0-98AF-5755340DDBE7}" name="Key"/>
+    <tableColumn id="6" xr3:uid="{5F994233-5BCF-45FB-BBDA-40FBBA46BAEA}" name="In design"/>
+    <tableColumn id="7" xr3:uid="{37B89A53-4BD6-4E86-89DF-BED82A595DD0}" name="On playfield"/>
+    <tableColumn id="8" xr3:uid="{540C323C-5E0E-4495-B1CF-D0B28C34B82F}" name="Action"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2693,17 +3339,17 @@
   <dimension ref="A1:K60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" customWidth="1"/>
     <col min="3" max="3" width="8.7265625" style="1"/>
-    <col min="4" max="4" width="10.6328125" customWidth="1"/>
-    <col min="5" max="5" width="14.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6328125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6328125" customWidth="1"/>
+    <col min="4" max="4" width="10.54296875" customWidth="1"/>
+    <col min="5" max="5" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.54296875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.54296875" customWidth="1"/>
     <col min="8" max="8" width="14.453125" customWidth="1"/>
     <col min="9" max="9" width="14.7265625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.54296875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="41.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
@@ -3482,6 +4128,2724 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67B9B565-78DA-42AC-A0D8-C5B614CDCC18}">
+  <dimension ref="B1:AR47"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2.81640625" customWidth="1"/>
+    <col min="2" max="2" width="14.54296875" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.81640625" style="15" customWidth="1"/>
+    <col min="5" max="5" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.81640625" style="15" customWidth="1"/>
+    <col min="10" max="10" width="11" style="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.54296875" style="17" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.81640625" customWidth="1"/>
+    <col min="13" max="13" width="14.54296875" style="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" style="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.81640625" style="15" customWidth="1"/>
+    <col min="16" max="16" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.81640625" style="15" customWidth="1"/>
+    <col min="21" max="21" width="11" style="17" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.54296875" style="17" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="2.81640625" customWidth="1"/>
+    <col min="24" max="24" width="14.54296875" style="15" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11" style="15" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.81640625" style="15" customWidth="1"/>
+    <col min="27" max="27" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.81640625" style="15" customWidth="1"/>
+    <col min="32" max="32" width="11" style="17" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.54296875" style="17" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="2.81640625" customWidth="1"/>
+    <col min="35" max="35" width="14.54296875" style="15" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11" style="15" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="5.81640625" style="15" customWidth="1"/>
+    <col min="38" max="38" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="4.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="5.81640625" style="15" customWidth="1"/>
+    <col min="43" max="43" width="11" style="17" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="14.54296875" style="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="B1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="T1" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="U1" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="V1" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="X1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y1" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z1" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="AE1" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="AF1" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG1" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="AJ1" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK1" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="AP1" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ1" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="AR1" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="2:44" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="C3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="N3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="T3" s="18"/>
+      <c r="U3" s="18"/>
+      <c r="Y3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB3" s="12"/>
+      <c r="AC3" s="12"/>
+      <c r="AD3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE3" s="18"/>
+      <c r="AF3" s="18"/>
+      <c r="AJ3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AM3" s="12"/>
+      <c r="AN3" s="12"/>
+      <c r="AO3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP3" s="18"/>
+      <c r="AQ3" s="18"/>
+    </row>
+    <row r="4" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="C4" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="N4" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="S4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="T4" s="18"/>
+      <c r="U4" s="18"/>
+      <c r="Y4" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE4" s="18"/>
+      <c r="AF4" s="18"/>
+      <c r="AJ4" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="AP4" s="18"/>
+      <c r="AQ4" s="18"/>
+    </row>
+    <row r="5" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="C5" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="N5" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="S5" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="T5" s="18"/>
+      <c r="U5" s="18"/>
+      <c r="Y5" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD5" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE5" s="18"/>
+      <c r="AF5" s="18"/>
+      <c r="AJ5" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO5" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AP5" s="18"/>
+      <c r="AQ5" s="18"/>
+    </row>
+    <row r="6" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="Y6" s="16"/>
+      <c r="Z6" s="16"/>
+      <c r="AA6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE6" s="18"/>
+      <c r="AF6" s="18"/>
+      <c r="AJ6" s="16"/>
+      <c r="AK6" s="16"/>
+      <c r="AL6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="AO6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP6" s="18"/>
+      <c r="AQ6" s="18"/>
+    </row>
+    <row r="7" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="B7" s="15" t="str">
+        <f>$G$41&amp;"-"&amp;H$32&amp;"-"&amp;D7</f>
+        <v>2-0-0</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="15">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="M7" s="15" t="str">
+        <f>$G$41&amp;"-"&amp;S$32&amp;"-"&amp;O7</f>
+        <v>2-1-0</v>
+      </c>
+      <c r="N7" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="O7" s="15">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="T7" s="18"/>
+      <c r="U7" s="18"/>
+      <c r="X7" s="15" t="str">
+        <f>$G$41&amp;"-"&amp;AD$32&amp;"-"&amp;Z7</f>
+        <v>2-2-0</v>
+      </c>
+      <c r="Y7" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z7" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE7" s="18"/>
+      <c r="AF7" s="18"/>
+      <c r="AI7" s="15" t="str">
+        <f>$G$41&amp;"-"&amp;AO$32&amp;"-"&amp;AK7</f>
+        <v>2-3-0</v>
+      </c>
+      <c r="AJ7" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK7" s="15">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AP7" s="18"/>
+      <c r="AQ7" s="18"/>
+    </row>
+    <row r="8" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="B8" s="15" t="str">
+        <f t="shared" ref="B8:B22" si="0">$G$41&amp;"-"&amp;H$32&amp;"-"&amp;D8</f>
+        <v>2-0-1</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="15">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="15">
+        <v>16</v>
+      </c>
+      <c r="J8" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K8" s="15" t="str">
+        <f>$G$41&amp;"-"&amp;H$32&amp;"-"&amp;I8</f>
+        <v>2-0-16</v>
+      </c>
+      <c r="M8" s="15" t="str">
+        <f t="shared" ref="M8:M22" si="1">$G$41&amp;"-"&amp;S$32&amp;"-"&amp;O8</f>
+        <v>2-1-1</v>
+      </c>
+      <c r="N8" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="O8" s="15">
+        <v>1</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="S8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="T8" s="15">
+        <v>16</v>
+      </c>
+      <c r="U8" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="V8" s="15" t="str">
+        <f>$G$41&amp;"-"&amp;S$32&amp;"-"&amp;T8</f>
+        <v>2-1-16</v>
+      </c>
+      <c r="X8" s="15" t="str">
+        <f t="shared" ref="X8:X22" si="2">$G$41&amp;"-"&amp;AD$32&amp;"-"&amp;Z8</f>
+        <v>2-2-1</v>
+      </c>
+      <c r="Y8" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z8" s="15">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE8" s="15">
+        <v>16</v>
+      </c>
+      <c r="AF8" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG8" s="27"/>
+      <c r="AI8" s="15" t="str">
+        <f t="shared" ref="AI8:AI22" si="3">$G$41&amp;"-"&amp;AO$32&amp;"-"&amp;AK8</f>
+        <v>2-3-1</v>
+      </c>
+      <c r="AJ8" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK8" s="15">
+        <v>1</v>
+      </c>
+      <c r="AL8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP8" s="15">
+        <v>16</v>
+      </c>
+      <c r="AQ8" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR8" s="15" t="str">
+        <f>$G$41&amp;"-"&amp;AO$32&amp;"-"&amp;AP8</f>
+        <v>2-3-16</v>
+      </c>
+    </row>
+    <row r="9" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="B9" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>2-0-2</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" s="15">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="15">
+        <v>17</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K9" s="15" t="str">
+        <f t="shared" ref="K9:K23" si="4">$G$41&amp;"-"&amp;H$32&amp;"-"&amp;I9</f>
+        <v>2-0-17</v>
+      </c>
+      <c r="M9" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>2-1-2</v>
+      </c>
+      <c r="N9" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="O9" s="15">
+        <v>2</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="T9" s="15">
+        <v>17</v>
+      </c>
+      <c r="U9" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="V9" s="15" t="str">
+        <f t="shared" ref="V9:V23" si="5">$G$41&amp;"-"&amp;S$32&amp;"-"&amp;T9</f>
+        <v>2-1-17</v>
+      </c>
+      <c r="X9" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>2-2-2</v>
+      </c>
+      <c r="Y9" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z9" s="15">
+        <v>2</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD9" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE9" s="15">
+        <v>17</v>
+      </c>
+      <c r="AF9" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG9" s="27"/>
+      <c r="AI9" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>2-3-2</v>
+      </c>
+      <c r="AJ9" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK9" s="15">
+        <v>2</v>
+      </c>
+      <c r="AL9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO9" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="AP9" s="15">
+        <v>17</v>
+      </c>
+      <c r="AQ9" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR9" s="15" t="str">
+        <f t="shared" ref="AR9:AR23" si="6">$G$41&amp;"-"&amp;AO$32&amp;"-"&amp;AP9</f>
+        <v>2-3-17</v>
+      </c>
+    </row>
+    <row r="10" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="B10" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>2-0-3</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="15">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" s="15">
+        <v>18</v>
+      </c>
+      <c r="J10" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K10" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>2-0-18</v>
+      </c>
+      <c r="M10" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>2-1-3</v>
+      </c>
+      <c r="N10" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="O10" s="15">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="T10" s="15">
+        <v>18</v>
+      </c>
+      <c r="U10" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="V10" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>2-1-18</v>
+      </c>
+      <c r="X10" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>2-2-3</v>
+      </c>
+      <c r="Y10" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z10" s="15">
+        <v>3</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE10" s="15">
+        <v>18</v>
+      </c>
+      <c r="AF10" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG10" s="27"/>
+      <c r="AI10" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>2-3-3</v>
+      </c>
+      <c r="AJ10" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK10" s="15">
+        <v>3</v>
+      </c>
+      <c r="AL10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="AP10" s="15">
+        <v>18</v>
+      </c>
+      <c r="AQ10" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR10" s="15" t="str">
+        <f t="shared" si="6"/>
+        <v>2-3-18</v>
+      </c>
+    </row>
+    <row r="11" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="B11" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>2-0-0</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="D11" s="15">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="15">
+        <v>19</v>
+      </c>
+      <c r="J11" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K11" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>2-0-19</v>
+      </c>
+      <c r="M11" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>2-1-0</v>
+      </c>
+      <c r="N11" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="O11" s="15">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T11" s="15">
+        <v>19</v>
+      </c>
+      <c r="U11" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="V11" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>2-1-19</v>
+      </c>
+      <c r="X11" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>2-2-4</v>
+      </c>
+      <c r="Y11" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z11" s="15">
+        <v>4</v>
+      </c>
+      <c r="AA11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE11" s="15">
+        <v>19</v>
+      </c>
+      <c r="AF11" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG11" s="27"/>
+      <c r="AI11" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>2-3-4</v>
+      </c>
+      <c r="AJ11" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK11" s="15">
+        <v>4</v>
+      </c>
+      <c r="AL11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP11" s="15">
+        <v>19</v>
+      </c>
+      <c r="AQ11" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR11" s="15" t="str">
+        <f t="shared" si="6"/>
+        <v>2-3-19</v>
+      </c>
+    </row>
+    <row r="12" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="B12" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>2-0-1</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="15">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" s="15">
+        <v>20</v>
+      </c>
+      <c r="J12" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K12" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>2-0-20</v>
+      </c>
+      <c r="M12" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>2-1-1</v>
+      </c>
+      <c r="N12" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="O12" s="15">
+        <v>1</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q12"/>
+      <c r="R12"/>
+      <c r="S12" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="T12" s="15">
+        <v>20</v>
+      </c>
+      <c r="U12" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="V12" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>2-1-20</v>
+      </c>
+      <c r="X12" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>2-2-5</v>
+      </c>
+      <c r="Y12" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z12" s="15">
+        <v>5</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB12"/>
+      <c r="AC12"/>
+      <c r="AD12" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE12" s="15">
+        <v>20</v>
+      </c>
+      <c r="AF12" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG12" s="27"/>
+      <c r="AI12" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>2-3-5</v>
+      </c>
+      <c r="AJ12" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK12" s="15">
+        <v>5</v>
+      </c>
+      <c r="AL12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM12"/>
+      <c r="AN12"/>
+      <c r="AO12" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP12" s="15">
+        <v>20</v>
+      </c>
+      <c r="AQ12" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR12" s="15" t="str">
+        <f t="shared" si="6"/>
+        <v>2-3-20</v>
+      </c>
+    </row>
+    <row r="13" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="B13" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>2-0-2</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="15">
+        <v>2</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I13" s="15">
+        <v>21</v>
+      </c>
+      <c r="J13" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K13" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>2-0-21</v>
+      </c>
+      <c r="M13" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>2-1-2</v>
+      </c>
+      <c r="N13" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="O13" s="15">
+        <v>2</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="T13" s="15">
+        <v>21</v>
+      </c>
+      <c r="U13" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="V13" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>2-1-21</v>
+      </c>
+      <c r="X13" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>2-2-6</v>
+      </c>
+      <c r="Y13" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z13" s="15">
+        <v>6</v>
+      </c>
+      <c r="AA13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE13" s="15">
+        <v>21</v>
+      </c>
+      <c r="AF13" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG13" s="27"/>
+      <c r="AI13" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>2-3-6</v>
+      </c>
+      <c r="AJ13" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK13" s="15">
+        <v>6</v>
+      </c>
+      <c r="AL13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AP13" s="15">
+        <v>21</v>
+      </c>
+      <c r="AQ13" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR13" s="15" t="str">
+        <f t="shared" si="6"/>
+        <v>2-3-21</v>
+      </c>
+    </row>
+    <row r="14" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="B14" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>2-0-3</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="D14" s="15">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" s="15">
+        <v>22</v>
+      </c>
+      <c r="J14" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K14" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>2-0-22</v>
+      </c>
+      <c r="M14" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>2-1-3</v>
+      </c>
+      <c r="N14" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="O14" s="15">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="T14" s="15">
+        <v>22</v>
+      </c>
+      <c r="U14" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="V14" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>2-1-22</v>
+      </c>
+      <c r="X14" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>2-2-7</v>
+      </c>
+      <c r="Y14" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z14" s="15">
+        <v>7</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE14" s="15">
+        <v>22</v>
+      </c>
+      <c r="AF14" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG14" s="27"/>
+      <c r="AI14" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>2-3-7</v>
+      </c>
+      <c r="AJ14" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK14" s="15">
+        <v>7</v>
+      </c>
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP14" s="15">
+        <v>22</v>
+      </c>
+      <c r="AQ14" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR14" s="15" t="str">
+        <f t="shared" si="6"/>
+        <v>2-3-22</v>
+      </c>
+    </row>
+    <row r="15" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="B15" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>2-0-8</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15" s="15">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="15">
+        <v>23</v>
+      </c>
+      <c r="J15" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K15" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>2-0-23</v>
+      </c>
+      <c r="M15" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>2-1-8</v>
+      </c>
+      <c r="N15" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="O15" s="15">
+        <v>8</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="S15" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T15" s="15">
+        <v>23</v>
+      </c>
+      <c r="U15" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="V15" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>2-1-23</v>
+      </c>
+      <c r="X15" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>2-2-8</v>
+      </c>
+      <c r="Y15" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z15" s="15">
+        <v>8</v>
+      </c>
+      <c r="AA15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD15" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE15" s="15">
+        <v>23</v>
+      </c>
+      <c r="AF15" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG15" s="27"/>
+      <c r="AI15" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>2-3-8</v>
+      </c>
+      <c r="AJ15" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK15" s="15">
+        <v>8</v>
+      </c>
+      <c r="AL15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO15" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AP15" s="15">
+        <v>23</v>
+      </c>
+      <c r="AQ15" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR15" s="15" t="str">
+        <f t="shared" si="6"/>
+        <v>2-3-23</v>
+      </c>
+    </row>
+    <row r="16" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="B16" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>2-0-9</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="D16" s="15">
+        <v>9</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="15">
+        <v>24</v>
+      </c>
+      <c r="J16" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K16" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>2-0-24</v>
+      </c>
+      <c r="M16" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>2-1-9</v>
+      </c>
+      <c r="N16" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="O16" s="15">
+        <v>9</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="T16" s="15">
+        <v>24</v>
+      </c>
+      <c r="U16" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="V16" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>2-1-24</v>
+      </c>
+      <c r="X16" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>2-2-9</v>
+      </c>
+      <c r="Y16" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z16" s="15">
+        <v>9</v>
+      </c>
+      <c r="AA16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE16" s="15">
+        <v>24</v>
+      </c>
+      <c r="AF16" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG16" s="27"/>
+      <c r="AI16" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>2-3-9</v>
+      </c>
+      <c r="AJ16" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK16" s="15">
+        <v>9</v>
+      </c>
+      <c r="AL16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="AP16" s="15">
+        <v>24</v>
+      </c>
+      <c r="AQ16" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR16" s="15" t="str">
+        <f t="shared" si="6"/>
+        <v>2-3-24</v>
+      </c>
+    </row>
+    <row r="17" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="B17" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>2-0-10</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="D17" s="15">
+        <v>10</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="15">
+        <v>25</v>
+      </c>
+      <c r="J17" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K17" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>2-0-25</v>
+      </c>
+      <c r="M17" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>2-1-10</v>
+      </c>
+      <c r="N17" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="O17" s="15">
+        <v>10</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S17" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="T17" s="15">
+        <v>25</v>
+      </c>
+      <c r="U17" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="V17" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>2-1-25</v>
+      </c>
+      <c r="X17" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>2-2-10</v>
+      </c>
+      <c r="Y17" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z17" s="15">
+        <v>10</v>
+      </c>
+      <c r="AA17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD17" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE17" s="15">
+        <v>25</v>
+      </c>
+      <c r="AF17" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG17" s="27"/>
+      <c r="AI17" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>2-3-10</v>
+      </c>
+      <c r="AJ17" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK17" s="15">
+        <v>10</v>
+      </c>
+      <c r="AL17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AO17" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="AP17" s="15">
+        <v>25</v>
+      </c>
+      <c r="AQ17" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR17" s="15" t="str">
+        <f t="shared" si="6"/>
+        <v>2-3-25</v>
+      </c>
+    </row>
+    <row r="18" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="B18" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>2-0-11</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="15">
+        <v>11</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="15">
+        <v>26</v>
+      </c>
+      <c r="J18" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K18" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>2-0-26</v>
+      </c>
+      <c r="M18" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>2-1-11</v>
+      </c>
+      <c r="N18" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="O18" s="15">
+        <v>11</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="S18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="T18" s="15">
+        <v>26</v>
+      </c>
+      <c r="U18" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="V18" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>2-1-26</v>
+      </c>
+      <c r="X18" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>2-2-11</v>
+      </c>
+      <c r="Y18" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z18" s="15">
+        <v>11</v>
+      </c>
+      <c r="AA18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE18" s="15">
+        <v>26</v>
+      </c>
+      <c r="AF18" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG18" s="27"/>
+      <c r="AI18" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>2-3-11</v>
+      </c>
+      <c r="AJ18" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK18" s="15">
+        <v>11</v>
+      </c>
+      <c r="AL18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP18" s="15">
+        <v>26</v>
+      </c>
+      <c r="AQ18" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR18" s="15" t="str">
+        <f t="shared" si="6"/>
+        <v>2-3-26</v>
+      </c>
+    </row>
+    <row r="19" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="B19" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>2-0-4</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="D19" s="15">
+        <v>4</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="15">
+        <v>27</v>
+      </c>
+      <c r="J19" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K19" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>2-0-27</v>
+      </c>
+      <c r="M19" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>2-1-4</v>
+      </c>
+      <c r="N19" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="O19" s="15">
+        <v>4</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="S19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="T19" s="15">
+        <v>27</v>
+      </c>
+      <c r="U19" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="V19" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>2-1-27</v>
+      </c>
+      <c r="X19" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>2-2-12</v>
+      </c>
+      <c r="Y19" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z19" s="15">
+        <v>12</v>
+      </c>
+      <c r="AA19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE19" s="15">
+        <v>27</v>
+      </c>
+      <c r="AF19" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG19" s="27"/>
+      <c r="AI19" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>2-3-12</v>
+      </c>
+      <c r="AJ19" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK19" s="15">
+        <v>12</v>
+      </c>
+      <c r="AL19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AP19" s="15">
+        <v>27</v>
+      </c>
+      <c r="AQ19" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR19" s="15" t="str">
+        <f t="shared" si="6"/>
+        <v>2-3-27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="B20" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>2-0-5</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="D20" s="15">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="15">
+        <v>28</v>
+      </c>
+      <c r="J20" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K20" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>2-0-28</v>
+      </c>
+      <c r="M20" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>2-1-5</v>
+      </c>
+      <c r="N20" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="O20" s="15">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="S20" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="T20" s="15">
+        <v>28</v>
+      </c>
+      <c r="U20" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="V20" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>2-1-28</v>
+      </c>
+      <c r="X20" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>2-2-13</v>
+      </c>
+      <c r="Y20" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z20" s="15">
+        <v>13</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD20" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE20" s="15">
+        <v>28</v>
+      </c>
+      <c r="AF20" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG20" s="27"/>
+      <c r="AI20" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>2-3-13</v>
+      </c>
+      <c r="AJ20" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK20" s="15">
+        <v>13</v>
+      </c>
+      <c r="AL20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO20" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP20" s="15">
+        <v>28</v>
+      </c>
+      <c r="AQ20" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR20" s="15" t="str">
+        <f t="shared" si="6"/>
+        <v>2-3-28</v>
+      </c>
+    </row>
+    <row r="21" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="B21" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>2-0-6</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" s="15">
+        <v>6</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I21" s="15">
+        <v>29</v>
+      </c>
+      <c r="J21" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K21" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>2-0-29</v>
+      </c>
+      <c r="M21" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>2-1-6</v>
+      </c>
+      <c r="N21" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="O21" s="15">
+        <v>6</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="S21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="T21" s="15">
+        <v>29</v>
+      </c>
+      <c r="U21" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="V21" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>2-1-29</v>
+      </c>
+      <c r="X21" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>2-2-14</v>
+      </c>
+      <c r="Y21" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z21" s="15">
+        <v>14</v>
+      </c>
+      <c r="AA21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE21" s="15">
+        <v>29</v>
+      </c>
+      <c r="AF21" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG21" s="27"/>
+      <c r="AI21" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>2-3-14</v>
+      </c>
+      <c r="AJ21" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK21" s="15">
+        <v>14</v>
+      </c>
+      <c r="AL21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="AP21" s="15">
+        <v>29</v>
+      </c>
+      <c r="AQ21" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR21" s="15" t="str">
+        <f t="shared" si="6"/>
+        <v>2-3-29</v>
+      </c>
+    </row>
+    <row r="22" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="B22" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>2-0-7</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="D22" s="15">
+        <v>7</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I22" s="15">
+        <v>30</v>
+      </c>
+      <c r="J22" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K22" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>2-0-30</v>
+      </c>
+      <c r="M22" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>2-1-7</v>
+      </c>
+      <c r="N22" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="O22" s="15">
+        <v>7</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T22" s="15">
+        <v>30</v>
+      </c>
+      <c r="U22" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="V22" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>2-1-30</v>
+      </c>
+      <c r="X22" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>2-2-15</v>
+      </c>
+      <c r="Y22" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z22" s="15">
+        <v>15</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE22" s="15">
+        <v>30</v>
+      </c>
+      <c r="AF22" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG22" s="27"/>
+      <c r="AI22" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>2-3-15</v>
+      </c>
+      <c r="AJ22" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK22" s="15">
+        <v>15</v>
+      </c>
+      <c r="AL22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP22" s="15">
+        <v>30</v>
+      </c>
+      <c r="AQ22" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR22" s="15" t="str">
+        <f t="shared" si="6"/>
+        <v>2-3-30</v>
+      </c>
+    </row>
+    <row r="23" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="15">
+        <v>31</v>
+      </c>
+      <c r="J23" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K23" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v>2-0-31</v>
+      </c>
+      <c r="N23" s="16"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="T23" s="15">
+        <v>31</v>
+      </c>
+      <c r="U23" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="V23" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>2-1-31</v>
+      </c>
+      <c r="Y23" s="16"/>
+      <c r="Z23" s="16"/>
+      <c r="AA23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE23" s="15">
+        <v>31</v>
+      </c>
+      <c r="AF23" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG23" s="27"/>
+      <c r="AJ23" s="16"/>
+      <c r="AK23" s="16"/>
+      <c r="AL23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AO23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP23" s="15">
+        <v>31</v>
+      </c>
+      <c r="AQ23" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR23" s="15" t="str">
+        <f t="shared" si="6"/>
+        <v>2-3-31</v>
+      </c>
+    </row>
+    <row r="24" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="S24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="T24" s="18"/>
+      <c r="U24" s="18"/>
+      <c r="Y24" s="16"/>
+      <c r="Z24" s="16"/>
+      <c r="AA24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE24" s="18"/>
+      <c r="AF24" s="18"/>
+      <c r="AJ24" s="16"/>
+      <c r="AK24" s="16"/>
+      <c r="AL24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="AP24" s="18"/>
+      <c r="AQ24" s="18"/>
+    </row>
+    <row r="25" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="E25" s="5"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="10"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="13"/>
+      <c r="S25" s="10"/>
+      <c r="AA25" s="5"/>
+      <c r="AB25" s="13"/>
+      <c r="AC25" s="13"/>
+      <c r="AD25" s="10"/>
+      <c r="AL25" s="5"/>
+      <c r="AM25" s="13"/>
+      <c r="AN25" s="13"/>
+      <c r="AO25" s="10"/>
+    </row>
+    <row r="26" spans="2:44" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="P26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R26" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="S26" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC26" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD26" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="AM26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN26" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="AO26" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="2:44" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="28" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="E28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q28" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="R28" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="S28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB28" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC28" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM28" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN28" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="AO28" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="E29" s="3"/>
+      <c r="H29" s="8"/>
+      <c r="P29" s="3"/>
+      <c r="S29" s="8"/>
+      <c r="AA29" s="3"/>
+      <c r="AD29" s="8"/>
+      <c r="AL29" s="3"/>
+      <c r="AO29" s="8"/>
+    </row>
+    <row r="30" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="E30" s="3"/>
+      <c r="H30" s="8"/>
+      <c r="P30" s="3"/>
+      <c r="S30" s="8"/>
+      <c r="AA30" s="3"/>
+      <c r="AD30" s="8"/>
+      <c r="AL30" s="3"/>
+      <c r="AO30" s="8"/>
+    </row>
+    <row r="31" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="E31" s="3"/>
+      <c r="F31" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31" s="43"/>
+      <c r="H31" s="8"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="R31" s="43"/>
+      <c r="S31" s="8"/>
+      <c r="AA31" s="3"/>
+      <c r="AB31" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC31" s="43"/>
+      <c r="AD31" s="8"/>
+      <c r="AL31" s="3"/>
+      <c r="AM31" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN31" s="43"/>
+      <c r="AO31" s="8"/>
+    </row>
+    <row r="32" spans="2:44" x14ac:dyDescent="0.35">
+      <c r="E32" s="3"/>
+      <c r="F32" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="H32" s="24">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="S32" s="24">
+        <f>H32+1</f>
+        <v>1</v>
+      </c>
+      <c r="AA32" s="3"/>
+      <c r="AB32" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD32" s="24">
+        <f>S32+1</f>
+        <v>2</v>
+      </c>
+      <c r="AL32" s="3"/>
+      <c r="AM32" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO32" s="24">
+        <f>AD32+1</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:41" x14ac:dyDescent="0.35">
+      <c r="E33" s="3"/>
+      <c r="H33" s="8"/>
+      <c r="P33" s="3"/>
+      <c r="S33" s="8"/>
+      <c r="AA33" s="3"/>
+      <c r="AD33" s="8"/>
+      <c r="AL33" s="3"/>
+      <c r="AO33" s="8"/>
+    </row>
+    <row r="34" spans="2:41" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E34" s="6"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="11"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="14"/>
+      <c r="R34" s="14"/>
+      <c r="S34" s="11"/>
+      <c r="AA34" s="6"/>
+      <c r="AB34" s="14"/>
+      <c r="AC34" s="14"/>
+      <c r="AD34" s="11"/>
+      <c r="AL34" s="6"/>
+      <c r="AM34" s="14"/>
+      <c r="AN34" s="14"/>
+      <c r="AO34" s="11"/>
+    </row>
+    <row r="35" spans="2:41" x14ac:dyDescent="0.35">
+      <c r="F35" s="2"/>
+      <c r="G35" s="7"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="7"/>
+      <c r="AB35" s="2"/>
+      <c r="AC35" s="7"/>
+      <c r="AM35" s="2"/>
+      <c r="AN35" s="7"/>
+    </row>
+    <row r="36" spans="2:41" x14ac:dyDescent="0.35">
+      <c r="F36" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="45"/>
+      <c r="Q36" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="R36" s="45"/>
+      <c r="AB36" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC36" s="45"/>
+      <c r="AM36" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN36" s="45"/>
+    </row>
+    <row r="37" spans="2:41" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F37" s="6"/>
+      <c r="G37" s="11"/>
+      <c r="Q37" s="6"/>
+      <c r="R37" s="11"/>
+      <c r="AB37" s="6"/>
+      <c r="AC37" s="11"/>
+      <c r="AM37" s="6"/>
+      <c r="AN37" s="11"/>
+    </row>
+    <row r="41" spans="2:41" x14ac:dyDescent="0.35">
+      <c r="E41" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="2:41" x14ac:dyDescent="0.35">
+      <c r="B43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="X43" s="17"/>
+      <c r="AI43" s="17"/>
+    </row>
+    <row r="44" spans="2:41" x14ac:dyDescent="0.35">
+      <c r="C44" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="G44" s="1" cm="1">
+        <f t="array" aca="1" ref="G44" ca="1">SUM(COUNTIF(INDIRECT({"$C$7:$C$22";"$J$8:$J$23";"$N$7:$N$22";"$U$8:$U$23";"$Y$7:$Y$22";"$AF$8:$AF$23";"$AJ$7:$AJ$22";"$AQ$8:$AQ$23"}),C44))</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:41" x14ac:dyDescent="0.35">
+      <c r="C45" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G45" s="1" cm="1">
+        <f t="array" aca="1" ref="G45" ca="1">SUM(COUNTIF(INDIRECT({"$C$7:$C$22";"$J$8:$J$23";"$N$7:$N$22";"$U$8:$U$23";"$Y$7:$Y$22";"$AF$8:$AF$23";"$AJ$7:$AJ$22";"$AQ$8:$AQ$23"}),C45))</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:41" x14ac:dyDescent="0.35">
+      <c r="C46" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="G46" s="1" cm="1">
+        <f t="array" aca="1" ref="G46" ca="1">SUM(COUNTIF(INDIRECT({"$C$7:$C$22";"$J$8:$J$23";"$N$7:$N$22";"$U$8:$U$23";"$Y$7:$Y$22";"$AF$8:$AF$23";"$AJ$7:$AJ$22";"$AQ$8:$AQ$23"}),C46))</f>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="2:41" x14ac:dyDescent="0.35">
+      <c r="C47" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="G47" s="1" cm="1">
+        <f t="array" aca="1" ref="G47" ca="1">SUM(COUNTIF(INDIRECT({"$C$7:$C$22";"$J$8:$J$23";"$N$7:$N$22";"$U$8:$U$23";"$Y$7:$Y$22";"$AF$8:$AF$23";"$AJ$7:$AJ$22";"$AQ$8:$AQ$23"}),C47))</f>
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="AB31:AC31"/>
+    <mergeCell ref="AB36:AC36"/>
+    <mergeCell ref="AM31:AN31"/>
+    <mergeCell ref="AM36:AN36"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="Q36:R36"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D32C0C9B-B0E5-442A-BA1C-E3DC79065275}">
+  <dimension ref="B1:K43"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="14" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.54296875" style="1" customWidth="1"/>
+    <col min="6" max="7" width="5.81640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10" style="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" style="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="D3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="18"/>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="D4" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="18"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="D5" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="18"/>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="D6" s="16"/>
+      <c r="E6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="18"/>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="E7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="18"/>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="E8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="E10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="E11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="E12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="46"/>
+      <c r="H12" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="E13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="E15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="E16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="E17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="E18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="E19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="E20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="E21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="E22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="D23" s="16"/>
+      <c r="E23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="D24" s="16"/>
+      <c r="E24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" s="18"/>
+    </row>
+    <row r="25" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="E25" s="5"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="10"/>
+    </row>
+    <row r="26" spans="4:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="4:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="28" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="E28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="E29" s="3"/>
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="E30" s="3"/>
+      <c r="H30" s="8"/>
+    </row>
+    <row r="31" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="E31" s="3"/>
+      <c r="F31" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31" s="43"/>
+      <c r="H31" s="8"/>
+    </row>
+    <row r="32" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="E32" s="3"/>
+      <c r="H32" s="8"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="E33" s="3"/>
+      <c r="H33" s="8"/>
+    </row>
+    <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E34" s="6"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="11"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="F35" s="2"/>
+      <c r="G35" s="7"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="F36" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="45"/>
+    </row>
+    <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F37" s="6"/>
+      <c r="G37" s="11"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B43" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F31:G31"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D4EE48-CA29-4AF5-8B5C-E4B4B1F31048}">
   <dimension ref="B28:B33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3517,42 +6881,42 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50ED5F98-D515-44A8-8822-0D97D946717D}">
   <dimension ref="B18:M19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="18" spans="2:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="47"/>
+      <c r="M18" s="47"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="46"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3565,7 +6929,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2780EF84-6B31-4EAC-80B5-D5D7A18FF689}">
   <dimension ref="B22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3583,144 +6947,456 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA66CEF0-BB4C-421C-91C0-863799021116}">
-  <dimension ref="B1:E20"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="52.6328125" customWidth="1"/>
-    <col min="5" max="5" width="17.1796875" customWidth="1"/>
+    <col min="1" max="1" width="12" style="17" customWidth="1"/>
+    <col min="2" max="2" width="14.54296875" customWidth="1"/>
+    <col min="3" max="3" width="66.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.26953125" customWidth="1"/>
+    <col min="7" max="7" width="12.81640625" customWidth="1"/>
+    <col min="8" max="8" width="30.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
+        <v>397</v>
+      </c>
       <c r="B1" t="s">
         <v>398</v>
       </c>
       <c r="C1" t="s">
-        <v>399</v>
+        <v>47</v>
       </c>
       <c r="D1" t="s">
-        <v>47</v>
+        <v>430</v>
       </c>
       <c r="E1" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
-        <v>397</v>
+      <c r="F1" t="s">
+        <v>446</v>
+      </c>
+      <c r="G1" t="s">
+        <v>420</v>
+      </c>
+      <c r="H1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="17" t="s">
+        <v>422</v>
+      </c>
+      <c r="C2" t="s">
+        <v>413</v>
       </c>
       <c r="D2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E2" s="41" t="s">
+        <v>422</v>
+      </c>
+      <c r="F2" s="41" t="s">
+        <v>421</v>
+      </c>
+      <c r="G2" s="41" t="s">
+        <v>421</v>
+      </c>
+      <c r="H2" s="41" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="C3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>424</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>421</v>
+      </c>
+      <c r="G3" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="17" t="s">
+        <v>436</v>
+      </c>
+      <c r="C4" t="s">
+        <v>441</v>
+      </c>
+      <c r="D4" t="s">
+        <v>442</v>
+      </c>
+      <c r="E4" s="42" t="s">
+        <v>436</v>
+      </c>
+      <c r="F4" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="G4" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="C5" t="s">
+        <v>438</v>
+      </c>
+      <c r="D5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>437</v>
+      </c>
+      <c r="F5" s="41" t="s">
+        <v>421</v>
+      </c>
+      <c r="G5" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="H5" s="42" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>423</v>
+      </c>
+      <c r="C6" t="s">
+        <v>412</v>
+      </c>
+      <c r="D6" t="s">
+        <v>417</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>423</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>421</v>
+      </c>
+      <c r="G6" s="41" t="s">
+        <v>421</v>
+      </c>
+      <c r="H6" s="42" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="C7" t="s">
+        <v>399</v>
+      </c>
+      <c r="D7" t="s">
+        <v>433</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>425</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>421</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>421</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="C8" t="s">
+        <v>448</v>
+      </c>
+      <c r="D8" t="s">
+        <v>433</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>447</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="G8" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="H8" s="42" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="17" t="s">
         <v>400</v>
       </c>
-      <c r="E2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
+      <c r="C9" t="s">
+        <v>403</v>
+      </c>
+      <c r="D9" t="s">
+        <v>431</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>400</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="G9" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="H9" s="42" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="17" t="s">
         <v>401</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C10" t="s">
+        <v>402</v>
+      </c>
+      <c r="D10" t="s">
+        <v>434</v>
+      </c>
+      <c r="E10" s="41" t="s">
+        <v>401</v>
+      </c>
+      <c r="F10" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="G10" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="H10" s="42" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="C11" t="s">
         <v>404</v>
       </c>
-      <c r="E4" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
-        <v>402</v>
-      </c>
-      <c r="D6" t="s">
-        <v>403</v>
-      </c>
-      <c r="E6" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B8" t="s">
+      <c r="D11" t="s">
+        <v>434</v>
+      </c>
+      <c r="E11" s="41" t="s">
+        <v>405</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="G11" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="H11" s="41" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="D8" t="s">
-        <v>405</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="C12" t="s">
+        <v>440</v>
+      </c>
+      <c r="D12" t="s">
+        <v>434</v>
+      </c>
+      <c r="E12" s="41" t="s">
+        <v>406</v>
+      </c>
+      <c r="F12" s="41" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B10" t="s">
+      <c r="G12" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="H12" s="41" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="17" t="s">
         <v>407</v>
       </c>
-      <c r="D10" t="s">
+      <c r="C13" t="s">
+        <v>408</v>
+      </c>
+      <c r="D13" t="s">
+        <v>414</v>
+      </c>
+      <c r="E13" s="41" t="s">
+        <v>407</v>
+      </c>
+      <c r="F13" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="G13" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="H13" s="42" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="17" t="s">
         <v>409</v>
       </c>
-      <c r="E10" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B12" t="s">
-        <v>408</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C14" t="s">
         <v>410</v>
       </c>
-      <c r="E12" t="s">
+      <c r="D14" t="s">
+        <v>415</v>
+      </c>
+      <c r="E14" s="41" t="s">
+        <v>409</v>
+      </c>
+      <c r="F14" s="41" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B14" t="s">
-        <v>411</v>
-      </c>
-      <c r="D14" t="s">
-        <v>412</v>
-      </c>
-      <c r="E14" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B16" t="s">
-        <v>413</v>
+      <c r="G14" s="41" t="s">
+        <v>421</v>
+      </c>
+      <c r="H14" s="41" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="C15" t="s">
+        <v>428</v>
+      </c>
+      <c r="D15" t="s">
+        <v>461</v>
+      </c>
+      <c r="E15" s="49" t="s">
+        <v>458</v>
+      </c>
+      <c r="F15" t="s">
+        <v>428</v>
+      </c>
+      <c r="G15" t="s">
+        <v>428</v>
+      </c>
+      <c r="H15" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="17" t="s">
+        <v>459</v>
+      </c>
+      <c r="C16" t="s">
+        <v>428</v>
       </c>
       <c r="D16" t="s">
-        <v>414</v>
-      </c>
-      <c r="E16" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B18" t="s">
-        <v>415</v>
-      </c>
-      <c r="D18" t="s">
-        <v>416</v>
-      </c>
-      <c r="E18" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B20" t="s">
-        <v>417</v>
-      </c>
-      <c r="D20" t="s">
-        <v>418</v>
-      </c>
-      <c r="E20" t="s">
-        <v>426</v>
+        <v>460</v>
+      </c>
+      <c r="E16" s="49" t="s">
+        <v>459</v>
+      </c>
+      <c r="F16" t="s">
+        <v>428</v>
+      </c>
+      <c r="G16" t="s">
+        <v>428</v>
+      </c>
+      <c r="H16" t="s">
+        <v>428</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ED65BC7-0492-4730-B230-1478A10E4A09}">
+  <dimension ref="C17:V27"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.35">
+      <c r="K17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.35">
+      <c r="Q19" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.35">
+      <c r="Q21" t="s">
+        <v>456</v>
+      </c>
+      <c r="V21" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.35">
+      <c r="C27" t="s">
+        <v>454</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB9F92C7-9560-4AE0-B9B9-53E8D3A5BB69}">
+  <dimension ref="B28:O28"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>451</v>
+      </c>
+      <c r="J28" t="s">
+        <v>452</v>
+      </c>
+      <c r="O28" t="s">
+        <v>462</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E848134-5BBE-40A2-B435-5EF431EA961E}">
   <dimension ref="B1:J51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3729,7 +7405,7 @@
     <col min="2" max="2" width="18.54296875" customWidth="1"/>
     <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.7265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="38.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.1796875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="2.81640625" customWidth="1"/>
     <col min="7" max="7" width="5.26953125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
@@ -4461,12 +8137,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64143CA7-704E-4C2D-9785-F0A4C7EA94D7}">
   <dimension ref="B2:DA44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="3.6328125" customWidth="1"/>
+    <col min="2" max="2" width="3.54296875" customWidth="1"/>
     <col min="3" max="3" width="25.81640625" customWidth="1"/>
     <col min="4" max="6" width="3.453125" customWidth="1"/>
     <col min="7" max="7" width="4" customWidth="1"/>
@@ -4478,7 +8154,7 @@
     <col min="27" max="45" width="2.1796875" customWidth="1"/>
     <col min="46" max="46" width="2.54296875" customWidth="1"/>
     <col min="47" max="68" width="2.1796875" customWidth="1"/>
-    <col min="71" max="71" width="11.90625" customWidth="1"/>
+    <col min="71" max="71" width="11.81640625" customWidth="1"/>
     <col min="76" max="84" width="3.54296875" customWidth="1"/>
     <col min="85" max="85" width="17.54296875" customWidth="1"/>
     <col min="86" max="94" width="3.54296875" customWidth="1"/>
@@ -4887,7 +8563,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{896D7F36-299A-4BDE-822D-D1A9A709E1EC}">
   <dimension ref="B1:AZ47"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7520,30 +11196,30 @@
     </row>
     <row r="31" spans="2:52" x14ac:dyDescent="0.35">
       <c r="F31" s="3"/>
-      <c r="G31" s="41" t="s">
+      <c r="G31" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="H31" s="41"/>
+      <c r="H31" s="43"/>
       <c r="I31" s="8"/>
       <c r="S31" s="3"/>
-      <c r="T31" s="41" t="str">
+      <c r="T31" s="43" t="str">
         <f>G31</f>
         <v>COM6</v>
       </c>
-      <c r="U31" s="41"/>
+      <c r="U31" s="43"/>
       <c r="V31" s="8"/>
       <c r="AF31" s="3"/>
-      <c r="AG31" s="41" t="str">
+      <c r="AG31" s="43" t="str">
         <f>T31</f>
         <v>COM6</v>
       </c>
-      <c r="AH31" s="41"/>
+      <c r="AH31" s="43"/>
       <c r="AI31" s="8"/>
       <c r="AS31" s="3"/>
-      <c r="AT31" s="41" t="s">
+      <c r="AT31" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="AU31" s="41"/>
+      <c r="AU31" s="43"/>
       <c r="AV31" s="8"/>
     </row>
     <row r="32" spans="2:52" x14ac:dyDescent="0.35">
@@ -7618,23 +11294,23 @@
       <c r="AU35" s="7"/>
     </row>
     <row r="36" spans="3:48" x14ac:dyDescent="0.35">
-      <c r="G36" s="42" t="s">
+      <c r="G36" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="H36" s="43"/>
-      <c r="T36" s="42" t="s">
+      <c r="H36" s="45"/>
+      <c r="T36" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="U36" s="43"/>
+      <c r="U36" s="45"/>
       <c r="Y36"/>
-      <c r="AG36" s="42" t="s">
+      <c r="AG36" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="AH36" s="43"/>
-      <c r="AT36" s="42" t="s">
+      <c r="AH36" s="45"/>
+      <c r="AT36" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="AU36" s="43"/>
+      <c r="AU36" s="45"/>
     </row>
     <row r="37" spans="3:48" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G37" s="6"/>
@@ -7737,7 +11413,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92BC837E-B245-42A3-8F6D-5B1D3622F670}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7746,7 +11422,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12CF9BA9-790E-4443-8CE6-3586A1333188}">
   <dimension ref="C1:DA109"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -8179,2722 +11855,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67B9B565-78DA-42AC-A0D8-C5B614CDCC18}">
-  <dimension ref="B1:AR47"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="2.81640625" customWidth="1"/>
-    <col min="2" max="2" width="14.54296875" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.81640625" style="15" customWidth="1"/>
-    <col min="5" max="5" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.81640625" style="15" customWidth="1"/>
-    <col min="10" max="10" width="11" style="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" style="17" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="2.81640625" customWidth="1"/>
-    <col min="13" max="13" width="14.54296875" style="15" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11" style="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.81640625" style="15" customWidth="1"/>
-    <col min="16" max="16" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.81640625" style="15" customWidth="1"/>
-    <col min="21" max="21" width="11" style="17" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.54296875" style="17" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="2.81640625" customWidth="1"/>
-    <col min="24" max="24" width="14.54296875" style="15" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11" style="15" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.81640625" style="15" customWidth="1"/>
-    <col min="27" max="27" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.81640625" style="15" customWidth="1"/>
-    <col min="32" max="32" width="11" style="17" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.54296875" style="17" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="2.81640625" customWidth="1"/>
-    <col min="35" max="35" width="14.54296875" style="15" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="11" style="15" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="5.81640625" style="15" customWidth="1"/>
-    <col min="38" max="38" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="4.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="5.81640625" style="15" customWidth="1"/>
-    <col min="43" max="43" width="11" style="17" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="14.54296875" style="17" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="B1" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="K1" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="T1" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="U1" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="V1" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="X1" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y1" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z1" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="AE1" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="AF1" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG1" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI1" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="AJ1" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK1" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="AP1" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="AQ1" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR1" s="17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="2:44" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="C3" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="N3" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="T3" s="18"/>
-      <c r="U3" s="18"/>
-      <c r="Y3" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB3" s="12"/>
-      <c r="AC3" s="12"/>
-      <c r="AD3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE3" s="18"/>
-      <c r="AF3" s="18"/>
-      <c r="AJ3" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AM3" s="12"/>
-      <c r="AN3" s="12"/>
-      <c r="AO3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="AP3" s="18"/>
-      <c r="AQ3" s="18"/>
-    </row>
-    <row r="4" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="C4" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="N4" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="S4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="T4" s="18"/>
-      <c r="U4" s="18"/>
-      <c r="Y4" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE4" s="18"/>
-      <c r="AF4" s="18"/>
-      <c r="AJ4" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="AL4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AO4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="AP4" s="18"/>
-      <c r="AQ4" s="18"/>
-    </row>
-    <row r="5" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="C5" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="N5" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="T5" s="18"/>
-      <c r="U5" s="18"/>
-      <c r="Y5" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE5" s="18"/>
-      <c r="AF5" s="18"/>
-      <c r="AJ5" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="AL5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="AP5" s="18"/>
-      <c r="AQ5" s="18"/>
-    </row>
-    <row r="6" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="S6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="T6" s="18"/>
-      <c r="U6" s="18"/>
-      <c r="Y6" s="16"/>
-      <c r="Z6" s="16"/>
-      <c r="AA6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE6" s="18"/>
-      <c r="AF6" s="18"/>
-      <c r="AJ6" s="16"/>
-      <c r="AK6" s="16"/>
-      <c r="AL6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="AO6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="AP6" s="18"/>
-      <c r="AQ6" s="18"/>
-    </row>
-    <row r="7" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="B7" s="15" t="str">
-        <f>$G$41&amp;"-"&amp;H$32&amp;"-"&amp;D7</f>
-        <v>2-0-0</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="D7" s="15">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="M7" s="15" t="str">
-        <f>$G$41&amp;"-"&amp;S$32&amp;"-"&amp;O7</f>
-        <v>2-1-0</v>
-      </c>
-      <c r="N7" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="O7" s="15">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="T7" s="18"/>
-      <c r="U7" s="18"/>
-      <c r="X7" s="15" t="str">
-        <f>$G$41&amp;"-"&amp;AD$32&amp;"-"&amp;Z7</f>
-        <v>2-2-0</v>
-      </c>
-      <c r="Y7" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z7" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD7" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE7" s="18"/>
-      <c r="AF7" s="18"/>
-      <c r="AI7" s="15" t="str">
-        <f>$G$41&amp;"-"&amp;AO$32&amp;"-"&amp;AK7</f>
-        <v>2-3-0</v>
-      </c>
-      <c r="AJ7" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK7" s="15">
-        <v>0</v>
-      </c>
-      <c r="AL7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO7" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AP7" s="18"/>
-      <c r="AQ7" s="18"/>
-    </row>
-    <row r="8" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="B8" s="15" t="str">
-        <f t="shared" ref="B8:B22" si="0">$G$41&amp;"-"&amp;H$32&amp;"-"&amp;D8</f>
-        <v>2-0-1</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="D8" s="15">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="15">
-        <v>16</v>
-      </c>
-      <c r="J8" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="K8" s="15" t="str">
-        <f>$G$41&amp;"-"&amp;H$32&amp;"-"&amp;I8</f>
-        <v>2-0-16</v>
-      </c>
-      <c r="M8" s="15" t="str">
-        <f t="shared" ref="M8:M22" si="1">$G$41&amp;"-"&amp;S$32&amp;"-"&amp;O8</f>
-        <v>2-1-1</v>
-      </c>
-      <c r="N8" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="O8" s="15">
-        <v>1</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="S8" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="T8" s="15">
-        <v>16</v>
-      </c>
-      <c r="U8" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="V8" s="15" t="str">
-        <f>$G$41&amp;"-"&amp;S$32&amp;"-"&amp;T8</f>
-        <v>2-1-16</v>
-      </c>
-      <c r="X8" s="15" t="str">
-        <f t="shared" ref="X8:X22" si="2">$G$41&amp;"-"&amp;AD$32&amp;"-"&amp;Z8</f>
-        <v>2-2-1</v>
-      </c>
-      <c r="Y8" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z8" s="15">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD8" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE8" s="15">
-        <v>16</v>
-      </c>
-      <c r="AF8" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG8" s="27"/>
-      <c r="AI8" s="15" t="str">
-        <f t="shared" ref="AI8:AI22" si="3">$G$41&amp;"-"&amp;AO$32&amp;"-"&amp;AK8</f>
-        <v>2-3-1</v>
-      </c>
-      <c r="AJ8" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK8" s="15">
-        <v>1</v>
-      </c>
-      <c r="AL8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO8" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP8" s="15">
-        <v>16</v>
-      </c>
-      <c r="AQ8" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR8" s="15" t="str">
-        <f>$G$41&amp;"-"&amp;AO$32&amp;"-"&amp;AP8</f>
-        <v>2-3-16</v>
-      </c>
-    </row>
-    <row r="9" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="B9" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>2-0-2</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="D9" s="15">
-        <v>2</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" s="15">
-        <v>17</v>
-      </c>
-      <c r="J9" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="K9" s="15" t="str">
-        <f t="shared" ref="K9:K23" si="4">$G$41&amp;"-"&amp;H$32&amp;"-"&amp;I9</f>
-        <v>2-0-17</v>
-      </c>
-      <c r="M9" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>2-1-2</v>
-      </c>
-      <c r="N9" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="O9" s="15">
-        <v>2</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S9" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="T9" s="15">
-        <v>17</v>
-      </c>
-      <c r="U9" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="V9" s="15" t="str">
-        <f t="shared" ref="V9:V23" si="5">$G$41&amp;"-"&amp;S$32&amp;"-"&amp;T9</f>
-        <v>2-1-17</v>
-      </c>
-      <c r="X9" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>2-2-2</v>
-      </c>
-      <c r="Y9" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z9" s="15">
-        <v>2</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD9" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE9" s="15">
-        <v>17</v>
-      </c>
-      <c r="AF9" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG9" s="27"/>
-      <c r="AI9" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>2-3-2</v>
-      </c>
-      <c r="AJ9" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK9" s="15">
-        <v>2</v>
-      </c>
-      <c r="AL9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO9" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="AP9" s="15">
-        <v>17</v>
-      </c>
-      <c r="AQ9" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR9" s="15" t="str">
-        <f t="shared" ref="AR9:AR23" si="6">$G$41&amp;"-"&amp;AO$32&amp;"-"&amp;AP9</f>
-        <v>2-3-17</v>
-      </c>
-    </row>
-    <row r="10" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="B10" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>2-0-3</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="D10" s="15">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I10" s="15">
-        <v>18</v>
-      </c>
-      <c r="J10" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="K10" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v>2-0-18</v>
-      </c>
-      <c r="M10" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>2-1-3</v>
-      </c>
-      <c r="N10" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="O10" s="15">
-        <v>3</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="T10" s="15">
-        <v>18</v>
-      </c>
-      <c r="U10" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="V10" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v>2-1-18</v>
-      </c>
-      <c r="X10" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>2-2-3</v>
-      </c>
-      <c r="Y10" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z10" s="15">
-        <v>3</v>
-      </c>
-      <c r="AA10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE10" s="15">
-        <v>18</v>
-      </c>
-      <c r="AF10" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG10" s="27"/>
-      <c r="AI10" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>2-3-3</v>
-      </c>
-      <c r="AJ10" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK10" s="15">
-        <v>3</v>
-      </c>
-      <c r="AL10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="AP10" s="15">
-        <v>18</v>
-      </c>
-      <c r="AQ10" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR10" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v>2-3-18</v>
-      </c>
-    </row>
-    <row r="11" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="B11" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>2-0-0</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="D11" s="15">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" s="15">
-        <v>19</v>
-      </c>
-      <c r="J11" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="K11" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v>2-0-19</v>
-      </c>
-      <c r="M11" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>2-1-0</v>
-      </c>
-      <c r="N11" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="O11" s="15">
-        <v>0</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S11" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="T11" s="15">
-        <v>19</v>
-      </c>
-      <c r="U11" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="V11" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v>2-1-19</v>
-      </c>
-      <c r="X11" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>2-2-4</v>
-      </c>
-      <c r="Y11" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z11" s="15">
-        <v>4</v>
-      </c>
-      <c r="AA11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD11" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE11" s="15">
-        <v>19</v>
-      </c>
-      <c r="AF11" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG11" s="27"/>
-      <c r="AI11" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>2-3-4</v>
-      </c>
-      <c r="AJ11" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK11" s="15">
-        <v>4</v>
-      </c>
-      <c r="AL11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO11" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP11" s="15">
-        <v>19</v>
-      </c>
-      <c r="AQ11" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR11" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v>2-3-19</v>
-      </c>
-    </row>
-    <row r="12" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="B12" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>2-0-1</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="D12" s="15">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" s="15">
-        <v>20</v>
-      </c>
-      <c r="J12" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="K12" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v>2-0-20</v>
-      </c>
-      <c r="M12" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>2-1-1</v>
-      </c>
-      <c r="N12" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="O12" s="15">
-        <v>1</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q12"/>
-      <c r="R12"/>
-      <c r="S12" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="T12" s="15">
-        <v>20</v>
-      </c>
-      <c r="U12" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="V12" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v>2-1-20</v>
-      </c>
-      <c r="X12" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>2-2-5</v>
-      </c>
-      <c r="Y12" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z12" s="15">
-        <v>5</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB12"/>
-      <c r="AC12"/>
-      <c r="AD12" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE12" s="15">
-        <v>20</v>
-      </c>
-      <c r="AF12" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG12" s="27"/>
-      <c r="AI12" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>2-3-5</v>
-      </c>
-      <c r="AJ12" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK12" s="15">
-        <v>5</v>
-      </c>
-      <c r="AL12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM12"/>
-      <c r="AN12"/>
-      <c r="AO12" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP12" s="15">
-        <v>20</v>
-      </c>
-      <c r="AQ12" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR12" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v>2-3-20</v>
-      </c>
-    </row>
-    <row r="13" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="B13" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>2-0-2</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="D13" s="15">
-        <v>2</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I13" s="15">
-        <v>21</v>
-      </c>
-      <c r="J13" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="K13" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v>2-0-21</v>
-      </c>
-      <c r="M13" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>2-1-2</v>
-      </c>
-      <c r="N13" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="O13" s="15">
-        <v>2</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="S13" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T13" s="15">
-        <v>21</v>
-      </c>
-      <c r="U13" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="V13" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v>2-1-21</v>
-      </c>
-      <c r="X13" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>2-2-6</v>
-      </c>
-      <c r="Y13" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z13" s="15">
-        <v>6</v>
-      </c>
-      <c r="AA13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD13" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE13" s="15">
-        <v>21</v>
-      </c>
-      <c r="AF13" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG13" s="27"/>
-      <c r="AI13" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>2-3-6</v>
-      </c>
-      <c r="AJ13" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK13" s="15">
-        <v>6</v>
-      </c>
-      <c r="AL13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO13" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="AP13" s="15">
-        <v>21</v>
-      </c>
-      <c r="AQ13" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR13" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v>2-3-21</v>
-      </c>
-    </row>
-    <row r="14" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="B14" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>2-0-3</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="D14" s="15">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="I14" s="15">
-        <v>22</v>
-      </c>
-      <c r="J14" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="K14" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v>2-0-22</v>
-      </c>
-      <c r="M14" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>2-1-3</v>
-      </c>
-      <c r="N14" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="O14" s="15">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="T14" s="15">
-        <v>22</v>
-      </c>
-      <c r="U14" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="V14" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v>2-1-22</v>
-      </c>
-      <c r="X14" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>2-2-7</v>
-      </c>
-      <c r="Y14" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z14" s="15">
-        <v>7</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD14" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE14" s="15">
-        <v>22</v>
-      </c>
-      <c r="AF14" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG14" s="27"/>
-      <c r="AI14" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>2-3-7</v>
-      </c>
-      <c r="AJ14" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK14" s="15">
-        <v>7</v>
-      </c>
-      <c r="AL14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AO14" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP14" s="15">
-        <v>22</v>
-      </c>
-      <c r="AQ14" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR14" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v>2-3-22</v>
-      </c>
-    </row>
-    <row r="15" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="B15" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>2-0-8</v>
-      </c>
-      <c r="C15" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="D15" s="15">
-        <v>8</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="15">
-        <v>23</v>
-      </c>
-      <c r="J15" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="K15" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v>2-0-23</v>
-      </c>
-      <c r="M15" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>2-1-8</v>
-      </c>
-      <c r="N15" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="O15" s="15">
-        <v>8</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="S15" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="T15" s="15">
-        <v>23</v>
-      </c>
-      <c r="U15" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="V15" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v>2-1-23</v>
-      </c>
-      <c r="X15" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>2-2-8</v>
-      </c>
-      <c r="Y15" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z15" s="15">
-        <v>8</v>
-      </c>
-      <c r="AA15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD15" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE15" s="15">
-        <v>23</v>
-      </c>
-      <c r="AF15" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG15" s="27"/>
-      <c r="AI15" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>2-3-8</v>
-      </c>
-      <c r="AJ15" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK15" s="15">
-        <v>8</v>
-      </c>
-      <c r="AL15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO15" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AP15" s="15">
-        <v>23</v>
-      </c>
-      <c r="AQ15" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR15" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v>2-3-23</v>
-      </c>
-    </row>
-    <row r="16" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="B16" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>2-0-9</v>
-      </c>
-      <c r="C16" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="D16" s="15">
-        <v>9</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" s="15">
-        <v>24</v>
-      </c>
-      <c r="J16" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="K16" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v>2-0-24</v>
-      </c>
-      <c r="M16" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>2-1-9</v>
-      </c>
-      <c r="N16" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="O16" s="15">
-        <v>9</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S16" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="T16" s="15">
-        <v>24</v>
-      </c>
-      <c r="U16" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="V16" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v>2-1-24</v>
-      </c>
-      <c r="X16" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>2-2-9</v>
-      </c>
-      <c r="Y16" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z16" s="15">
-        <v>9</v>
-      </c>
-      <c r="AA16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD16" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE16" s="15">
-        <v>24</v>
-      </c>
-      <c r="AF16" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG16" s="27"/>
-      <c r="AI16" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>2-3-9</v>
-      </c>
-      <c r="AJ16" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK16" s="15">
-        <v>9</v>
-      </c>
-      <c r="AL16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO16" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="AP16" s="15">
-        <v>24</v>
-      </c>
-      <c r="AQ16" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR16" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v>2-3-24</v>
-      </c>
-    </row>
-    <row r="17" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="B17" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>2-0-10</v>
-      </c>
-      <c r="C17" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="D17" s="15">
-        <v>10</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I17" s="15">
-        <v>25</v>
-      </c>
-      <c r="J17" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="K17" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v>2-0-25</v>
-      </c>
-      <c r="M17" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>2-1-10</v>
-      </c>
-      <c r="N17" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="O17" s="15">
-        <v>10</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="S17" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="T17" s="15">
-        <v>25</v>
-      </c>
-      <c r="U17" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="V17" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v>2-1-25</v>
-      </c>
-      <c r="X17" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>2-2-10</v>
-      </c>
-      <c r="Y17" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z17" s="15">
-        <v>10</v>
-      </c>
-      <c r="AA17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD17" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE17" s="15">
-        <v>25</v>
-      </c>
-      <c r="AF17" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG17" s="27"/>
-      <c r="AI17" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>2-3-10</v>
-      </c>
-      <c r="AJ17" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK17" s="15">
-        <v>10</v>
-      </c>
-      <c r="AL17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AO17" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="AP17" s="15">
-        <v>25</v>
-      </c>
-      <c r="AQ17" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR17" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v>2-3-25</v>
-      </c>
-    </row>
-    <row r="18" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="B18" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>2-0-11</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="D18" s="15">
-        <v>11</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="15">
-        <v>26</v>
-      </c>
-      <c r="J18" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="K18" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v>2-0-26</v>
-      </c>
-      <c r="M18" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>2-1-11</v>
-      </c>
-      <c r="N18" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="O18" s="15">
-        <v>11</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S18" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="T18" s="15">
-        <v>26</v>
-      </c>
-      <c r="U18" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="V18" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v>2-1-26</v>
-      </c>
-      <c r="X18" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>2-2-11</v>
-      </c>
-      <c r="Y18" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z18" s="15">
-        <v>11</v>
-      </c>
-      <c r="AA18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD18" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE18" s="15">
-        <v>26</v>
-      </c>
-      <c r="AF18" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG18" s="27"/>
-      <c r="AI18" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>2-3-11</v>
-      </c>
-      <c r="AJ18" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK18" s="15">
-        <v>11</v>
-      </c>
-      <c r="AL18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AO18" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP18" s="15">
-        <v>26</v>
-      </c>
-      <c r="AQ18" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR18" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v>2-3-26</v>
-      </c>
-    </row>
-    <row r="19" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="B19" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>2-0-4</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="D19" s="15">
-        <v>4</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="15">
-        <v>27</v>
-      </c>
-      <c r="J19" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="K19" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v>2-0-27</v>
-      </c>
-      <c r="M19" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>2-1-4</v>
-      </c>
-      <c r="N19" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="O19" s="15">
-        <v>4</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="S19" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="T19" s="15">
-        <v>27</v>
-      </c>
-      <c r="U19" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="V19" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v>2-1-27</v>
-      </c>
-      <c r="X19" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>2-2-12</v>
-      </c>
-      <c r="Y19" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z19" s="15">
-        <v>12</v>
-      </c>
-      <c r="AA19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD19" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="AE19" s="15">
-        <v>27</v>
-      </c>
-      <c r="AF19" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG19" s="27"/>
-      <c r="AI19" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>2-3-12</v>
-      </c>
-      <c r="AJ19" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK19" s="15">
-        <v>12</v>
-      </c>
-      <c r="AL19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="AO19" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="AP19" s="15">
-        <v>27</v>
-      </c>
-      <c r="AQ19" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR19" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v>2-3-27</v>
-      </c>
-    </row>
-    <row r="20" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="B20" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>2-0-5</v>
-      </c>
-      <c r="C20" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="D20" s="15">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="15">
-        <v>28</v>
-      </c>
-      <c r="J20" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="K20" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v>2-0-28</v>
-      </c>
-      <c r="M20" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>2-1-5</v>
-      </c>
-      <c r="N20" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="O20" s="15">
-        <v>5</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="S20" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="T20" s="15">
-        <v>28</v>
-      </c>
-      <c r="U20" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="V20" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v>2-1-28</v>
-      </c>
-      <c r="X20" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>2-2-13</v>
-      </c>
-      <c r="Y20" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z20" s="15">
-        <v>13</v>
-      </c>
-      <c r="AA20" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD20" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE20" s="15">
-        <v>28</v>
-      </c>
-      <c r="AF20" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG20" s="27"/>
-      <c r="AI20" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>2-3-13</v>
-      </c>
-      <c r="AJ20" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK20" s="15">
-        <v>13</v>
-      </c>
-      <c r="AL20" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="AO20" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="AP20" s="15">
-        <v>28</v>
-      </c>
-      <c r="AQ20" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR20" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v>2-3-28</v>
-      </c>
-    </row>
-    <row r="21" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="B21" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>2-0-6</v>
-      </c>
-      <c r="C21" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="D21" s="15">
-        <v>6</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="I21" s="15">
-        <v>29</v>
-      </c>
-      <c r="J21" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="K21" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v>2-0-29</v>
-      </c>
-      <c r="M21" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>2-1-6</v>
-      </c>
-      <c r="N21" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="O21" s="15">
-        <v>6</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="S21" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="T21" s="15">
-        <v>29</v>
-      </c>
-      <c r="U21" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="V21" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v>2-1-29</v>
-      </c>
-      <c r="X21" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>2-2-14</v>
-      </c>
-      <c r="Y21" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z21" s="15">
-        <v>14</v>
-      </c>
-      <c r="AA21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD21" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE21" s="15">
-        <v>29</v>
-      </c>
-      <c r="AF21" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG21" s="27"/>
-      <c r="AI21" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>2-3-14</v>
-      </c>
-      <c r="AJ21" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK21" s="15">
-        <v>14</v>
-      </c>
-      <c r="AL21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="AO21" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="AP21" s="15">
-        <v>29</v>
-      </c>
-      <c r="AQ21" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR21" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v>2-3-29</v>
-      </c>
-    </row>
-    <row r="22" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="B22" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>2-0-7</v>
-      </c>
-      <c r="C22" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="D22" s="15">
-        <v>7</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I22" s="15">
-        <v>30</v>
-      </c>
-      <c r="J22" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="K22" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v>2-0-30</v>
-      </c>
-      <c r="M22" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>2-1-7</v>
-      </c>
-      <c r="N22" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="O22" s="15">
-        <v>7</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S22" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T22" s="15">
-        <v>30</v>
-      </c>
-      <c r="U22" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="V22" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v>2-1-30</v>
-      </c>
-      <c r="X22" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>2-2-15</v>
-      </c>
-      <c r="Y22" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z22" s="15">
-        <v>15</v>
-      </c>
-      <c r="AA22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD22" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AE22" s="15">
-        <v>30</v>
-      </c>
-      <c r="AF22" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG22" s="27"/>
-      <c r="AI22" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>2-3-15</v>
-      </c>
-      <c r="AJ22" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK22" s="15">
-        <v>15</v>
-      </c>
-      <c r="AL22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AO22" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AP22" s="15">
-        <v>30</v>
-      </c>
-      <c r="AQ22" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR22" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v>2-3-30</v>
-      </c>
-    </row>
-    <row r="23" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I23" s="15">
-        <v>31</v>
-      </c>
-      <c r="J23" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="K23" s="15" t="str">
-        <f t="shared" si="4"/>
-        <v>2-0-31</v>
-      </c>
-      <c r="N23" s="16"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="S23" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="T23" s="15">
-        <v>31</v>
-      </c>
-      <c r="U23" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="V23" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v>2-1-31</v>
-      </c>
-      <c r="Y23" s="16"/>
-      <c r="Z23" s="16"/>
-      <c r="AA23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD23" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE23" s="15">
-        <v>31</v>
-      </c>
-      <c r="AF23" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG23" s="27"/>
-      <c r="AJ23" s="16"/>
-      <c r="AK23" s="16"/>
-      <c r="AL23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AO23" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="AP23" s="15">
-        <v>31</v>
-      </c>
-      <c r="AQ23" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR23" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v>2-3-31</v>
-      </c>
-    </row>
-    <row r="24" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="S24" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="T24" s="18"/>
-      <c r="U24" s="18"/>
-      <c r="Y24" s="16"/>
-      <c r="Z24" s="16"/>
-      <c r="AA24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD24" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE24" s="18"/>
-      <c r="AF24" s="18"/>
-      <c r="AJ24" s="16"/>
-      <c r="AK24" s="16"/>
-      <c r="AL24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO24" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="AP24" s="18"/>
-      <c r="AQ24" s="18"/>
-    </row>
-    <row r="25" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="E25" s="5"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="10"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="13"/>
-      <c r="R25" s="13"/>
-      <c r="S25" s="10"/>
-      <c r="AA25" s="5"/>
-      <c r="AB25" s="13"/>
-      <c r="AC25" s="13"/>
-      <c r="AD25" s="10"/>
-      <c r="AL25" s="5"/>
-      <c r="AM25" s="13"/>
-      <c r="AN25" s="13"/>
-      <c r="AO25" s="10"/>
-    </row>
-    <row r="26" spans="2:44" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E26" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="P26" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q26" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="R26" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="S26" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA26" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB26" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC26" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD26" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL26" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="AM26" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="AN26" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="AO26" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="2:44" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="28" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="E28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q28" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="R28" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S28" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB28" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC28" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD28" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="AM28" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AN28" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="AO28" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="E29" s="3"/>
-      <c r="H29" s="8"/>
-      <c r="P29" s="3"/>
-      <c r="S29" s="8"/>
-      <c r="AA29" s="3"/>
-      <c r="AD29" s="8"/>
-      <c r="AL29" s="3"/>
-      <c r="AO29" s="8"/>
-    </row>
-    <row r="30" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="E30" s="3"/>
-      <c r="H30" s="8"/>
-      <c r="P30" s="3"/>
-      <c r="S30" s="8"/>
-      <c r="AA30" s="3"/>
-      <c r="AD30" s="8"/>
-      <c r="AL30" s="3"/>
-      <c r="AO30" s="8"/>
-    </row>
-    <row r="31" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="E31" s="3"/>
-      <c r="F31" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="G31" s="41"/>
-      <c r="H31" s="8"/>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="R31" s="41"/>
-      <c r="S31" s="8"/>
-      <c r="AA31" s="3"/>
-      <c r="AB31" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC31" s="41"/>
-      <c r="AD31" s="8"/>
-      <c r="AL31" s="3"/>
-      <c r="AM31" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="AN31" s="41"/>
-      <c r="AO31" s="8"/>
-    </row>
-    <row r="32" spans="2:44" x14ac:dyDescent="0.35">
-      <c r="E32" s="3"/>
-      <c r="F32" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="H32" s="24">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="S32" s="24">
-        <f>H32+1</f>
-        <v>1</v>
-      </c>
-      <c r="AA32" s="3"/>
-      <c r="AB32" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="AD32" s="24">
-        <f>S32+1</f>
-        <v>2</v>
-      </c>
-      <c r="AL32" s="3"/>
-      <c r="AM32" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="AO32" s="24">
-        <f>AD32+1</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.35">
-      <c r="E33" s="3"/>
-      <c r="H33" s="8"/>
-      <c r="P33" s="3"/>
-      <c r="S33" s="8"/>
-      <c r="AA33" s="3"/>
-      <c r="AD33" s="8"/>
-      <c r="AL33" s="3"/>
-      <c r="AO33" s="8"/>
-    </row>
-    <row r="34" spans="2:41" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E34" s="6"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="11"/>
-      <c r="P34" s="6"/>
-      <c r="Q34" s="14"/>
-      <c r="R34" s="14"/>
-      <c r="S34" s="11"/>
-      <c r="AA34" s="6"/>
-      <c r="AB34" s="14"/>
-      <c r="AC34" s="14"/>
-      <c r="AD34" s="11"/>
-      <c r="AL34" s="6"/>
-      <c r="AM34" s="14"/>
-      <c r="AN34" s="14"/>
-      <c r="AO34" s="11"/>
-    </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.35">
-      <c r="F35" s="2"/>
-      <c r="G35" s="7"/>
-      <c r="Q35" s="2"/>
-      <c r="R35" s="7"/>
-      <c r="AB35" s="2"/>
-      <c r="AC35" s="7"/>
-      <c r="AM35" s="2"/>
-      <c r="AN35" s="7"/>
-    </row>
-    <row r="36" spans="2:41" x14ac:dyDescent="0.35">
-      <c r="F36" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="43"/>
-      <c r="Q36" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="R36" s="43"/>
-      <c r="AB36" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC36" s="43"/>
-      <c r="AM36" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN36" s="43"/>
-    </row>
-    <row r="37" spans="2:41" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F37" s="6"/>
-      <c r="G37" s="11"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="11"/>
-      <c r="AB37" s="6"/>
-      <c r="AC37" s="11"/>
-      <c r="AM37" s="6"/>
-      <c r="AN37" s="11"/>
-    </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.35">
-      <c r="E41" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.35">
-      <c r="B43" s="17"/>
-      <c r="M43" s="17"/>
-      <c r="X43" s="17"/>
-      <c r="AI43" s="17"/>
-    </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.35">
-      <c r="C44" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="G44" s="1" cm="1">
-        <f t="array" aca="1" ref="G44" ca="1">SUM(COUNTIF(INDIRECT({"$C$7:$C$22";"$J$8:$J$23";"$N$7:$N$22";"$U$8:$U$23";"$Y$7:$Y$22";"$AF$8:$AF$23";"$AJ$7:$AJ$22";"$AQ$8:$AQ$23"}),C44))</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.35">
-      <c r="C45" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="G45" s="1" cm="1">
-        <f t="array" aca="1" ref="G45" ca="1">SUM(COUNTIF(INDIRECT({"$C$7:$C$22";"$J$8:$J$23";"$N$7:$N$22";"$U$8:$U$23";"$Y$7:$Y$22";"$AF$8:$AF$23";"$AJ$7:$AJ$22";"$AQ$8:$AQ$23"}),C45))</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.35">
-      <c r="C46" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="G46" s="1" cm="1">
-        <f t="array" aca="1" ref="G46" ca="1">SUM(COUNTIF(INDIRECT({"$C$7:$C$22";"$J$8:$J$23";"$N$7:$N$22";"$U$8:$U$23";"$Y$7:$Y$22";"$AF$8:$AF$23";"$AJ$7:$AJ$22";"$AQ$8:$AQ$23"}),C46))</f>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.35">
-      <c r="C47" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="G47" s="1" cm="1">
-        <f t="array" aca="1" ref="G47" ca="1">SUM(COUNTIF(INDIRECT({"$C$7:$C$22";"$J$8:$J$23";"$N$7:$N$22";"$U$8:$U$23";"$Y$7:$Y$22";"$AF$8:$AF$23";"$AJ$7:$AJ$22";"$AQ$8:$AQ$23"}),C47))</f>
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="AB31:AC31"/>
-    <mergeCell ref="AB36:AC36"/>
-    <mergeCell ref="AM31:AN31"/>
-    <mergeCell ref="AM36:AN36"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="Q36:R36"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D32C0C9B-B0E5-442A-BA1C-E3DC79065275}">
-  <dimension ref="B1:K43"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="14" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.54296875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="5.81640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.453125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10" style="17" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" style="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14" style="17" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B1" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="I1" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="K1" s="17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="D3" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="18"/>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="D4" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="18"/>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="D5" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="18"/>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="D6" s="16"/>
-      <c r="E6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="I6" s="18"/>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="E7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="18"/>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="E8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="E11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="E12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" s="44"/>
-      <c r="H12" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="E13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="E15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="E16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="4:9" x14ac:dyDescent="0.35">
-      <c r="E17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="4:9" x14ac:dyDescent="0.35">
-      <c r="E18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="4:9" x14ac:dyDescent="0.35">
-      <c r="E19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="4:9" x14ac:dyDescent="0.35">
-      <c r="E20" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="4:9" x14ac:dyDescent="0.35">
-      <c r="E21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="4:9" x14ac:dyDescent="0.35">
-      <c r="E22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="4:9" x14ac:dyDescent="0.35">
-      <c r="D23" s="16"/>
-      <c r="E23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="4:9" x14ac:dyDescent="0.35">
-      <c r="D24" s="16"/>
-      <c r="E24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24" s="18"/>
-    </row>
-    <row r="25" spans="4:9" x14ac:dyDescent="0.35">
-      <c r="E25" s="5"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="10"/>
-    </row>
-    <row r="26" spans="4:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E26" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="4:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="28" spans="4:9" x14ac:dyDescent="0.35">
-      <c r="E28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="4:9" x14ac:dyDescent="0.35">
-      <c r="E29" s="3"/>
-      <c r="H29" s="8"/>
-    </row>
-    <row r="30" spans="4:9" x14ac:dyDescent="0.35">
-      <c r="E30" s="3"/>
-      <c r="H30" s="8"/>
-    </row>
-    <row r="31" spans="4:9" x14ac:dyDescent="0.35">
-      <c r="E31" s="3"/>
-      <c r="F31" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="G31" s="41"/>
-      <c r="H31" s="8"/>
-    </row>
-    <row r="32" spans="4:9" x14ac:dyDescent="0.35">
-      <c r="E32" s="3"/>
-      <c r="H32" s="8"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="E33" s="3"/>
-      <c r="H33" s="8"/>
-    </row>
-    <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E34" s="6"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="11"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="F35" s="2"/>
-      <c r="G35" s="7"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="F36" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="43"/>
-    </row>
-    <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F37" s="6"/>
-      <c r="G37" s="11"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B43" s="17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F31:G31"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>